--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484089_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484089_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.8106</v>
+        <v>3.2734</v>
       </c>
       <c r="E2" t="n">
-        <v>2.8095</v>
+        <v>3.0759</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0011</v>
+        <v>0.1974</v>
       </c>
       <c r="G2" t="n">
         <v>1.1675</v>
@@ -610,13 +610,13 @@
         <v>0.7935</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3055</v>
+        <v>0.1573</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1643</v>
+        <v>0.1021</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1412</v>
+        <v>0.0552</v>
       </c>
       <c r="V2" t="n">
         <v>2.1469</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>L. NDIAYE</t>
+          <t>V. CEBRIA PUCHADES</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.4011</v>
+        <v>0.6764</v>
       </c>
       <c r="E3" t="n">
-        <v>2.4046</v>
+        <v>1.3151</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.0035</v>
+        <v>-0.6387</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0256</v>
+        <v>0.5201</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.1586</v>
+        <v>0.3529</v>
       </c>
       <c r="I3" t="n">
-        <v>1.1842</v>
+        <v>0.1671</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.0774</v>
+        <v>1.8907</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.8405</v>
+        <v>1.2054</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7631</v>
+        <v>0.6853</v>
       </c>
       <c r="M3" t="n">
-        <v>0.103</v>
+        <v>-1.3707</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.3181</v>
+        <v>-0.8525</v>
       </c>
       <c r="O3" t="n">
-        <v>0.4211</v>
+        <v>-0.5182</v>
       </c>
       <c r="P3" t="n">
+        <v>1.1903</v>
+      </c>
+      <c r="Q3" t="n">
         <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>-1.1903</v>
       </c>
       <c r="R3" t="n">
         <v>1.1903</v>
       </c>
       <c r="S3" t="n">
-        <v>1.9074</v>
+        <v>-0.0935</v>
       </c>
       <c r="T3" t="n">
-        <v>2.4658</v>
+        <v>-0.5044</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5584</v>
+        <v>0.4108</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.532</v>
+        <v>-0.9405</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2065</v>
+        <v>-0.0713</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.7384</v>
+        <v>-0.8692</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>V. CEBRIA PUCHADES</t>
+          <t>F. PASCUAL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7915</v>
+        <v>0.6394</v>
       </c>
       <c r="E4" t="n">
-        <v>1.5985</v>
+        <v>0.52</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.8070000000000001</v>
+        <v>0.1195</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5201</v>
+        <v>0.0755</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3529</v>
+        <v>-1.6178</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1671</v>
+        <v>1.6933</v>
       </c>
       <c r="J4" t="n">
-        <v>1.8907</v>
+        <v>0.605</v>
       </c>
       <c r="K4" t="n">
-        <v>1.2054</v>
+        <v>-0.6802</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6853</v>
+        <v>1.2852</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.3707</v>
+        <v>-0.5295</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.8525</v>
+        <v>-0.9376</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.5182</v>
+        <v>0.4081</v>
       </c>
       <c r="P4" t="n">
-        <v>1.1903</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
+        <v>-0.1984</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.1984</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.2267</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.1134</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.1133</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.3373</v>
+      </c>
+      <c r="W4" t="n">
         <v>0</v>
       </c>
-      <c r="R4" t="n">
-        <v>1.1903</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0.0216</v>
-      </c>
-      <c r="T4" t="n">
-        <v>-0.2209</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0.2425</v>
-      </c>
-      <c r="V4" t="n">
-        <v>-0.9405</v>
-      </c>
-      <c r="W4" t="n">
-        <v>-0.0713</v>
-      </c>
       <c r="X4" t="n">
-        <v>-0.8692</v>
+        <v>0.3373</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>F. PASCUAL</t>
+          <t>L. NDIAYE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3629</v>
+        <v>0.0959</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3556</v>
+        <v>0.9591</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0073</v>
+        <v>-0.8632</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0755</v>
+        <v>0.0256</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.6178</v>
+        <v>-1.1586</v>
       </c>
       <c r="I5" t="n">
-        <v>1.6933</v>
+        <v>1.1842</v>
       </c>
       <c r="J5" t="n">
-        <v>0.605</v>
+        <v>-0.0774</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.6802</v>
+        <v>-0.8405</v>
       </c>
       <c r="L5" t="n">
-        <v>1.2852</v>
+        <v>0.7631</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5295</v>
+        <v>0.103</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.9376</v>
+        <v>-0.3181</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4081</v>
+        <v>0.4211</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.1984</v>
+        <v>-1.1903</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1984</v>
+        <v>1.1903</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0499</v>
+        <v>0.6022999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.051</v>
+        <v>1.0204</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0011</v>
+        <v>-0.4181</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3373</v>
+        <v>-0.532</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.2065</v>
       </c>
       <c r="X5" t="n">
-        <v>0.3373</v>
+        <v>-1.7384</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2984</v>
+        <v>-0.1059</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5582</v>
+        <v>0.7226</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.8566</v>
+        <v>-0.8285</v>
       </c>
       <c r="G6" t="n">
         <v>0.2862</v>
@@ -922,13 +922,13 @@
         <v>0.3968</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3781</v>
+        <v>-0.1856</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1247</v>
+        <v>0.0397</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2534</v>
+        <v>-0.2253</v>
       </c>
       <c r="V6" t="n">
         <v>-0.6032</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. CASTILLO EDIO</t>
+          <t>D. MARTIN VELA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.9486</v>
+        <v>-1.4983</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.5895</v>
+        <v>-2.0922</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6409</v>
+        <v>0.5938</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.8056</v>
+        <v>-2.9471</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.8523</v>
+        <v>-1.8498</v>
       </c>
       <c r="I7" t="n">
-        <v>1.0468</v>
+        <v>-1.0974</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6322</v>
+        <v>-2.4995</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.0622</v>
+        <v>-0.5794</v>
       </c>
       <c r="L7" t="n">
-        <v>1.6944</v>
+        <v>-1.9201</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.4378</v>
+        <v>-0.4477</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.7901</v>
+        <v>-1.2704</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.6477000000000001</v>
+        <v>0.8227</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.3968</v>
+        <v>-0.7935</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.1822</v>
+        <v>-1.1903</v>
       </c>
       <c r="R7" t="n">
-        <v>1.7855</v>
+        <v>0.3968</v>
       </c>
       <c r="S7" t="n">
-        <v>1.2538</v>
+        <v>0.3614</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0395</v>
+        <v>0.3912</v>
       </c>
       <c r="U7" t="n">
-        <v>1.2933</v>
+        <v>-0.0298</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.881</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.2065</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>0.6745</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. MARTIN VELA</t>
+          <t>P. GUASCH BENLLOCH</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.6449</v>
+        <v>-1.575</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.1545</v>
+        <v>-1.5332</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5096000000000001</v>
+        <v>-0.0418</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.9471</v>
+        <v>-1.6165</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.8498</v>
+        <v>-1.1592</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.0974</v>
+        <v>-0.4573</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.4995</v>
+        <v>-1.1591</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.5794</v>
+        <v>-0.5592</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.9201</v>
+        <v>-0.5999</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4477</v>
+        <v>-0.4574</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.2704</v>
+        <v>-0.6</v>
       </c>
       <c r="O8" t="n">
-        <v>0.8227</v>
+        <v>0.1425</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.7935</v>
+        <v>0.9919</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1903</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3968</v>
+        <v>0.9919</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2148</v>
+        <v>-0.6844</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3288</v>
+        <v>-0.3741</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.114</v>
+        <v>-0.3104</v>
       </c>
       <c r="V8" t="n">
-        <v>1.881</v>
+        <v>-0.266</v>
       </c>
       <c r="W8" t="n">
-        <v>1.2065</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.6745</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. GUASCH BENLLOCH</t>
+          <t>A. CASTILLO EDIO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.7776</v>
+        <v>-1.7971</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.5955</v>
+        <v>-1.7086</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1821</v>
+        <v>-0.0885</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.6165</v>
+        <v>-1.8056</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.1592</v>
+        <v>-2.8523</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4573</v>
+        <v>1.0468</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.1591</v>
+        <v>0.6322</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.5592</v>
+        <v>-1.0622</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.5999</v>
+        <v>1.6944</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.4574</v>
+        <v>-2.4378</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6</v>
+        <v>-1.7901</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1425</v>
+        <v>-0.6477000000000001</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9919</v>
+        <v>-0.3968</v>
       </c>
       <c r="Q9" t="n">
+        <v>-2.1822</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.7855</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.4053</v>
+      </c>
+      <c r="T9" t="n">
+        <v>-0.1586</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.5638</v>
+      </c>
+      <c r="V9" t="n">
         <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0.9919</v>
-      </c>
-      <c r="S9" t="n">
-        <v>-0.8871</v>
-      </c>
-      <c r="T9" t="n">
-        <v>-0.4364</v>
-      </c>
-      <c r="U9" t="n">
-        <v>-0.4506</v>
-      </c>
-      <c r="V9" t="n">
-        <v>-0.266</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.266</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.1905</v>
+        <v>-2.1031</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.9115</v>
+        <v>-1.9083</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.279</v>
+        <v>-0.1948</v>
       </c>
       <c r="G10" t="n">
         <v>-2.6741</v>
@@ -1234,13 +1234,13 @@
         <v>1.3887</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7147</v>
+        <v>0.3727</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.1505</v>
+        <v>-0.1472</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4358</v>
+        <v>0.5199</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.0241</v>
+        <v>-4.4338</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.7637</v>
+        <v>-4.0892</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2605</v>
+        <v>-0.3446</v>
       </c>
       <c r="G11" t="n">
         <v>-3.97</v>
@@ -1312,13 +1312,13 @@
         <v>0.9919</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.3201</v>
+        <v>-0.7298</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.3716</v>
+        <v>-0.6971000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0515</v>
+        <v>-0.0327</v>
       </c>
       <c r="V11" t="n">
         <v>0.266</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.8027</v>
+        <v>-5.2457</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.136</v>
+        <v>-3.4389</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.6666</v>
+        <v>-1.8069</v>
       </c>
       <c r="G12" t="n">
         <v>-1.9119</v>
@@ -1390,13 +1390,13 @@
         <v>1.5871</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.2442</v>
+        <v>-0.6873</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.3602</v>
+        <v>-0.6631</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1161</v>
+        <v>-0.0242</v>
       </c>
       <c r="V12" t="n">
         <v>-0.266</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-13.3207</v>
+        <v>-12.0738</v>
       </c>
       <c r="E13" t="n">
-        <v>-9.424299999999999</v>
+        <v>-8.1777</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.8964</v>
+        <v>-3.8963</v>
       </c>
       <c r="G13" t="n">
         <v>-12.8503</v>
@@ -1441,7 +1441,7 @@
         <v>-2.7208</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.758899999999999</v>
+        <v>-2.7589</v>
       </c>
       <c r="K13" t="n">
         <v>-2.563899999999999</v>
@@ -1453,7 +1453,7 @@
         <v>-10.0915</v>
       </c>
       <c r="N13" t="n">
-        <v>-7.5658</v>
+        <v>-7.565799999999999</v>
       </c>
       <c r="O13" t="n">
         <v>-2.5259</v>
@@ -1468,13 +1468,13 @@
         <v>10.9112</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.502</v>
+        <v>-0.2549000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.1245</v>
+        <v>-0.8777000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6226999999999998</v>
+        <v>0.6225000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>2.0235</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.073</v>
+        <v>6.9005</v>
       </c>
       <c r="E14" t="n">
-        <v>6.6876</v>
+        <v>5.4633</v>
       </c>
       <c r="F14" t="n">
-        <v>1.3854</v>
+        <v>1.4372</v>
       </c>
       <c r="G14" t="n">
         <v>4.5251</v>
@@ -1546,13 +1546,13 @@
         <v>1.9838</v>
       </c>
       <c r="S14" t="n">
-        <v>2.0014</v>
+        <v>0.8289</v>
       </c>
       <c r="T14" t="n">
-        <v>1.5362</v>
+        <v>0.3119</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4652</v>
+        <v>0.5171</v>
       </c>
       <c r="V14" t="n">
         <v>1.5465</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.3534</v>
+        <v>5.7384</v>
       </c>
       <c r="E15" t="n">
-        <v>3.463</v>
+        <v>4.0752</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8903</v>
+        <v>1.6632</v>
       </c>
       <c r="G15" t="n">
         <v>6.5548</v>
@@ -1624,13 +1624,13 @@
         <v>1.7855</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.2079</v>
+        <v>0.1771</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.2469</v>
+        <v>-0.6347</v>
       </c>
       <c r="U15" t="n">
-        <v>0.039</v>
+        <v>0.8119</v>
       </c>
       <c r="V15" t="n">
         <v>-0.7952</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.3079</v>
+        <v>4.1547</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2104</v>
+        <v>0.3125</v>
       </c>
       <c r="F16" t="n">
-        <v>3.0975</v>
+        <v>3.8423</v>
       </c>
       <c r="G16" t="n">
         <v>2.3859</v>
@@ -1702,13 +1702,13 @@
         <v>1.5871</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4217</v>
+        <v>0.4251</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1926</v>
+        <v>-0.0906</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2291</v>
+        <v>0.5157</v>
       </c>
       <c r="V16" t="n">
         <v>0.7486</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.6458</v>
+        <v>3.1611</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.7609</v>
+        <v>-0.1488</v>
       </c>
       <c r="F17" t="n">
-        <v>3.4067</v>
+        <v>3.3099</v>
       </c>
       <c r="G17" t="n">
         <v>2.3607</v>
@@ -1780,13 +1780,13 @@
         <v>1.1903</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2073</v>
+        <v>0.7226</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8728</v>
+        <v>-0.2607</v>
       </c>
       <c r="U17" t="n">
-        <v>1.0802</v>
+        <v>0.9833</v>
       </c>
       <c r="V17" t="n">
         <v>-0.1206</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.5414</v>
+        <v>2.7837</v>
       </c>
       <c r="E18" t="n">
-        <v>1.9741</v>
+        <v>2.0762</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5672</v>
+        <v>0.7075</v>
       </c>
       <c r="G18" t="n">
         <v>2.1082</v>
@@ -1858,13 +1858,13 @@
         <v>0.3968</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2296</v>
+        <v>0.0127</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.187</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0425</v>
+        <v>0.0978</v>
       </c>
       <c r="V18" t="n">
         <v>0.266</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.3697</v>
+        <v>2.2694</v>
       </c>
       <c r="E19" t="n">
-        <v>1.9231</v>
+        <v>1.7191</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4466</v>
+        <v>0.5504</v>
       </c>
       <c r="G19" t="n">
         <v>3.5464</v>
@@ -1936,13 +1936,13 @@
         <v>1.3887</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5736</v>
+        <v>0.4733</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3005</v>
+        <v>0.0965</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2731</v>
+        <v>0.3768</v>
       </c>
       <c r="V19" t="n">
         <v>-2.1469</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.2184</v>
+        <v>1.3587</v>
       </c>
       <c r="E20" t="n">
         <v>1.0163</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2021</v>
+        <v>0.3424</v>
       </c>
       <c r="G20" t="n">
         <v>-0.9488</v>
@@ -2014,13 +2014,13 @@
         <v>1.1903</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2296</v>
+        <v>-0.0893</v>
       </c>
       <c r="T20" t="n">
         <v>0.1191</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3486</v>
+        <v>-0.2084</v>
       </c>
       <c r="V20" t="n">
         <v>1.2065</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0596</v>
+        <v>-0.7483</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.5618</v>
+        <v>-2.378</v>
       </c>
       <c r="F21" t="n">
-        <v>1.5022</v>
+        <v>1.6297</v>
       </c>
       <c r="G21" t="n">
         <v>-0.8297</v>
@@ -2092,13 +2092,13 @@
         <v>1.3887</v>
       </c>
       <c r="S21" t="n">
-        <v>1.7004</v>
+        <v>1.0117</v>
       </c>
       <c r="T21" t="n">
-        <v>0.9184</v>
+        <v>0.1021</v>
       </c>
       <c r="U21" t="n">
-        <v>0.782</v>
+        <v>0.9096</v>
       </c>
       <c r="V21" t="n">
         <v>-1.3271</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.432</v>
+        <v>-4.8096</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.7688</v>
+        <v>-4.2587</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6632</v>
+        <v>-0.5508999999999999</v>
       </c>
       <c r="G22" t="n">
         <v>-3.7898</v>
@@ -2170,13 +2170,13 @@
         <v>0.3968</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7811</v>
+        <v>-0.1587</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4364</v>
+        <v>0.0737</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3447</v>
+        <v>-0.2324</v>
       </c>
       <c r="V22" t="n">
         <v>-0.266</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.6973</v>
+        <v>-5.4473</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.2867</v>
+        <v>-3.9806</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.4106</v>
+        <v>-1.4667</v>
       </c>
       <c r="G23" t="n">
         <v>-3.0623</v>
@@ -2248,13 +2248,13 @@
         <v>0.5952</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1111</v>
+        <v>0.1389</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5611</v>
+        <v>-0.255</v>
       </c>
       <c r="U23" t="n">
-        <v>0.45</v>
+        <v>0.3939</v>
       </c>
       <c r="V23" t="n">
         <v>-1.1352</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>13.32069999999999</v>
+        <v>15.3613</v>
       </c>
       <c r="E24" t="n">
-        <v>3.8963</v>
+        <v>3.8965</v>
       </c>
       <c r="F24" t="n">
-        <v>9.424199999999999</v>
+        <v>11.465</v>
       </c>
       <c r="G24" t="n">
         <v>12.8505</v>
@@ -2326,13 +2326,13 @@
         <v>11.9032</v>
       </c>
       <c r="S24" t="n">
-        <v>1.5017</v>
+        <v>3.5423</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6225999999999998</v>
+        <v>-0.6227</v>
       </c>
       <c r="U24" t="n">
-        <v>2.1246</v>
+        <v>4.1653</v>
       </c>
       <c r="V24" t="n">
         <v>-2.0234</v>
